--- a/registration_forms/048_language_test_booking_form--registration_forms.xlsx
+++ b/registration_forms/048_language_test_booking_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>language_test_booking_form</t>
+          <t>language_select</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -528,11 +528,7 @@
           <t>Select Language</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Choose a language</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -555,11 +551,7 @@
           <t>Name</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Enter the name of the candidate</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -597,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>candidate_phone</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -620,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>language_test_booking_form_schedule</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -628,11 +620,7 @@
           <t>Select Schedule</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Select a schedule</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -642,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language</t>
+          <t>appointment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Choose Language</t>
+          <t>Book an appointment</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -665,24 +653,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>language_test_booking_form_appointment</t>
+          <t>language</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Book an appointment</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Select an appointment</t>
-        </is>
-      </c>
+          <t>Choose Language</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -692,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>language_test_booking_form_time</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Select Time</t>
+          <t>Additional Info</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -715,24 +699,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>language_test_booking_form_additional_info</t>
+          <t>terms_agreement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Additional Info</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Enter any additional information</t>
-        </is>
-      </c>
+          <t>I agree to terms and conditions</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -742,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>language_test_booking_form_terms</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>I agree to terms and conditions</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -765,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>language_test_booking_form_note</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Enter Phone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -793,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>language_test_booking_form_phone</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enter Phone</t>
+          <t>Enter Email</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -811,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>language_test_booking_form_email</t>
+          <t>schedule2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Enter Email</t>
+          <t>Schedule2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language</t>
+          <t>appointment2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Choose Language</t>
+          <t>Appointment2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -857,24 +837,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>language_test_booking_form_schedule</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Select Schedule</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Select a schedule</t>
-        </is>
-      </c>
+          <t>Select Time</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -884,24 +860,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>language_test_booking_form_appointment</t>
+          <t>additional_info2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Book an Appointment</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Select an appointment</t>
-        </is>
-      </c>
+          <t>Additional Info2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>language_test_booking_form_time</t>
+          <t>terms_agreement2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Select Time</t>
+          <t>Terms Agreement2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,236 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>language_test_booking_form_additional_info</t>
+          <t>notes2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Additional Info</t>
+          <t>Notes2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_terms</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>I Agree to Terms and Conditions</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_note</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_phone</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Enter Phone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_email</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Enter Email</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_language</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Choose Language</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select Schedule</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Select a schedule</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_appointment</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Book an Appointment</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Select an appointment</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_time</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Select Time</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_additional_info</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Additional Info</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1180,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1208,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>language_test_booking_form_choices</t>
+          <t>language_select_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1225,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>language_test_booking_form_choices</t>
+          <t>language_select_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1242,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>language_test_booking_form_choices</t>
+          <t>language_select_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1259,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>language_test_booking_form_choices</t>
+          <t>language_select_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1276,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>language_test_booking_form_choices</t>
+          <t>language_select_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1293,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>language_test_booking_form_choices</t>
+          <t>language_select_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1310,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>language_test_booking_form_schedule_choices</t>
+          <t>schedule_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1327,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>language_test_booking_form_schedule_choices</t>
+          <t>schedule_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,7 +1101,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>language_test_booking_form_schedule_choices</t>
+          <t>schedule_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1361,7 +1118,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>language_test_booking_form_schedule_choices</t>
+          <t>schedule_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1378,7 +1135,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>language_test_booking_form_schedule_choices</t>
+          <t>schedule_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1395,7 +1152,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>language_test_booking_form_schedule_choices</t>
+          <t>schedule_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1412,7 +1169,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1429,7 +1186,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1446,7 +1203,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1463,7 +1220,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1480,7 +1237,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1497,7 +1254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1514,7 +1271,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>language_test_booking_form_terms_choices</t>
+          <t>terms_agreement_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1531,7 +1288,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>language_test_booking_form_terms_choices</t>
+          <t>terms_agreement_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1548,442 +1305,136 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>schedule2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>9am-5pm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>9am-5pm</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>schedule2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>5pm-9pm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>5pm-9pm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>schedule2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>10am-6pm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>10am-6pm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>schedule2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>11am-7pm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>11am-7pm</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>schedule2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>arabic</t>
+          <t>12pm-8pm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>12pm-8pm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>language_test_booking_form_language_choices</t>
+          <t>schedule2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>japanese</t>
+          <t>1pm-9pm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>1pm-9pm</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>language_test_booking_form_schedule_choices</t>
+          <t>terms_agreement2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9am-5pm</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9am-5pm</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>language_test_booking_form_schedule_choices</t>
+          <t>terms_agreement2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5pm-9pm</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5pm-9pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>10am-6pm</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>10am-6pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>11am-7pm</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>11am-7pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>12pm-8pm</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>12pm-8pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1pm-9pm</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1pm-9pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_terms_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_terms_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
           <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_language_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>french</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>French</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_language_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>english</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_language_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>spanish</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Spanish</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_language_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>chinese</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Chinese</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_language_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>arabic</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Arabic</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_language_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>japanese</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Japanese</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>9am-5pm</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>9am-5pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>5pm-9pm</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>5pm-9pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>10am-6pm</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>10am-6pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>11am-7pm</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>11am-7pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>12pm-8pm</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>12pm-8pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>language_test_booking_form_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1pm-9pm</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1pm-9pm</t>
         </is>
       </c>
     </row>
